--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:26:54+00:00</t>
+    <t>2025-01-23T13:26:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T13:26:37+00:00</t>
+    <t>2025-01-24T17:22:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T17:22:23+00:00</t>
+    <t>2025-01-29T14:25:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T14:25:50+00:00</t>
+    <t>2025-01-29T15:50:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T15:50:40+00:00</t>
+    <t>2025-01-30T15:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T15:03:39+00:00</t>
+    <t>2025-01-31T08:45:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T08:45:39+00:00</t>
+    <t>2025-02-18T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1912" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079" uniqueCount="252">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T10:06:11+00:00</t>
+    <t>2025-02-18T11:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>LegalAuthenticator représente les caractéristiques du professionnel et/ou de l'établissement participant.</t>
+    <t>L'élément de l'en-tête du CDA legalAuthenticator permet de représenter les caractéristiques du professionnel et/ou de l'établissement participant.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -636,7 +636,40 @@
     <t>LegalAuthenticator.assignedEntity.id</t>
   </si>
   <si>
+    <t>Identifiant du responsable</t>
+  </si>
+  <si>
     <t>AssignedEntity.id</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.id.nullFlavor</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.id.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.id.displayable</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.id.root</t>
+  </si>
+  <si>
+    <t>- Pour un professionnel : '1.2.250.1.71.4.2.1'
+- Pour le patient/usager : OID de l'autorité d'affectation de l'INS
+- Pour un système de structure : '1.2.250.1.71.4.2.1' 
+- Pour un SNR : OID de l'éditeur 
+- Pour le DP : '1.2.250.1.71.4.2.1'</t>
+  </si>
+  <si>
+    <t>A unique identifier that guarantees the global uniqueness of the instance identifier. The root alone may be the entire instance identifier.</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.id.extension</t>
+  </si>
+  <si>
+    <t>Valeur de l’identifiant.
+- Pour le PS, valeur de PS_IdNat (voir CI-SIS_ANX_SOURCES-DONNEES-PERSONNES-STRUCTURES).
+- Pour le patient/usager, valeur de l'INS du patient/usager.</t>
   </si>
   <si>
     <t>LegalAuthenticator.assignedEntity.sdtcIdentifiedBy</t>
@@ -656,6 +689,9 @@
 </t>
   </si>
   <si>
+    <t>Profession ou rôle du responsable</t>
+  </si>
+  <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS</t>
   </si>
   <si>
@@ -702,6 +738,9 @@
 </t>
   </si>
   <si>
+    <t>Adresse géopostale</t>
+  </si>
+  <si>
     <t>AssignedEntity.addr</t>
   </si>
   <si>
@@ -712,6 +751,9 @@
 </t>
   </si>
   <si>
+    <t>Coordonnées télécom</t>
+  </si>
+  <si>
     <t>AssignedEntity.telecom</t>
   </si>
   <si>
@@ -722,6 +764,13 @@
 </t>
   </si>
   <si>
+    <t>Personne physique : 
+- Obligatoire pour un professionnel 
+- Obligatoire pour un patient/usager 
+- Non utilisé pour un SNR 
+- Non utilisé pour le DP</t>
+  </si>
+  <si>
     <t>AssignedEntity.assignedPerson</t>
   </si>
   <si>
@@ -730,6 +779,11 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Organization {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-represented-organization}
 </t>
+  </si>
+  <si>
+    <t>Structure de rattachement :
+- Pour un PS : Organisation pour le compte de laquelle intervient le PS.
+- Pour un patient : seul l'élément standardIndustryClassCode est renseigné (cas particulier des documents d'expression personnelle du patient).</t>
   </si>
   <si>
     <t>AssignedEntity.representedOrganization</t>
@@ -1050,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK60"/>
+  <dimension ref="A1:AK65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.19140625" customWidth="true" bestFit="true"/>
@@ -5195,7 +5249,9 @@
       <c r="K41" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L41" s="2"/>
+      <c r="L41" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5246,7 +5302,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -5266,16 +5322,18 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E42" s="2"/>
+      <c r="E42" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
@@ -5292,10 +5350,12 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>204</v>
+        <v>85</v>
       </c>
       <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
+      <c r="M42" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5321,13 +5381,11 @@
         <v>74</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>74</v>
@@ -5345,13 +5403,13 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>205</v>
+        <v>89</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>74</v>
@@ -5365,21 +5423,23 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E43" s="2"/>
+      <c r="E43" t="s" s="2">
+        <v>100</v>
+      </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>74</v>
@@ -5391,10 +5451,12 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>207</v>
+        <v>101</v>
       </c>
       <c r="L43" s="2"/>
-      <c r="M43" s="2"/>
+      <c r="M43" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -5420,11 +5482,13 @@
         <v>74</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>208</v>
+        <v>74</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>74</v>
@@ -5442,7 +5506,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>209</v>
+        <v>103</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5462,17 +5526,17 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -5490,11 +5554,11 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5521,11 +5585,13 @@
         <v>74</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z44" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>74</v>
@@ -5543,7 +5609,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5563,20 +5629,20 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>62</v>
+        <v>110</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>75</v>
@@ -5591,11 +5657,13 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L45" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="M45" t="s" s="2">
-        <v>143</v>
+        <v>209</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5646,7 +5714,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5666,20 +5734,20 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>75</v>
@@ -5694,11 +5762,13 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L46" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="M46" t="s" s="2">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5749,7 +5819,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -5769,23 +5839,21 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E47" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>74</v>
@@ -5797,12 +5865,10 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>101</v>
+        <v>213</v>
       </c>
       <c r="L47" s="2"/>
-      <c r="M47" t="s" s="2">
-        <v>151</v>
-      </c>
+      <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -5852,13 +5918,13 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>152</v>
+        <v>214</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>74</v>
@@ -5872,23 +5938,21 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E48" t="s" s="2">
-        <v>154</v>
-      </c>
+      <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>74</v>
@@ -5900,12 +5964,12 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L48" s="2"/>
-      <c r="M48" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -5931,13 +5995,11 @@
         <v>74</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>74</v>
+        <v>218</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>74</v>
@@ -5955,7 +6017,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>156</v>
+        <v>219</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -5975,23 +6037,23 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>158</v>
+        <v>84</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>74</v>
@@ -6003,11 +6065,11 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>159</v>
+        <v>86</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6034,13 +6096,11 @@
         <v>74</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>74</v>
@@ -6058,7 +6118,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>160</v>
+        <v>89</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6078,21 +6138,23 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E50" s="2"/>
+      <c r="E50" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>74</v>
@@ -6104,11 +6166,11 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>162</v>
+        <v>85</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6159,7 +6221,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6179,21 +6241,23 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E51" s="2"/>
+      <c r="E51" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>74</v>
@@ -6205,11 +6269,11 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6260,7 +6324,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6280,17 +6344,17 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>80</v>
@@ -6308,11 +6372,11 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>170</v>
+        <v>101</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6363,7 +6427,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6383,17 +6447,17 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>80</v>
@@ -6411,11 +6475,11 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>175</v>
+        <v>101</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" t="s" s="2">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6466,13 +6530,13 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>74</v>
@@ -6486,23 +6550,23 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>74</v>
@@ -6514,11 +6578,11 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>180</v>
+        <v>101</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" t="s" s="2">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6569,13 +6633,13 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>74</v>
@@ -6589,10 +6653,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6603,7 +6667,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>74</v>
@@ -6615,10 +6679,12 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>222</v>
+        <v>162</v>
       </c>
       <c r="L55" s="2"/>
-      <c r="M55" s="2"/>
+      <c r="M55" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -6668,13 +6734,13 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>223</v>
+        <v>164</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>74</v>
@@ -6688,10 +6754,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6702,7 +6768,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>74</v>
@@ -6714,10 +6780,12 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>225</v>
+        <v>101</v>
       </c>
       <c r="L56" s="2"/>
-      <c r="M56" s="2"/>
+      <c r="M56" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -6767,13 +6835,13 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>226</v>
+        <v>167</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>74</v>
@@ -6787,16 +6855,18 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E57" s="2"/>
+      <c r="E57" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
@@ -6813,10 +6883,12 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>228</v>
+        <v>170</v>
       </c>
       <c r="L57" s="2"/>
-      <c r="M57" s="2"/>
+      <c r="M57" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -6866,7 +6938,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>229</v>
+        <v>172</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -6886,21 +6958,23 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E58" s="2"/>
+      <c r="E58" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>74</v>
@@ -6912,10 +6986,12 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>231</v>
+        <v>175</v>
       </c>
       <c r="L58" s="2"/>
-      <c r="M58" s="2"/>
+      <c r="M58" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -6965,13 +7041,13 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>232</v>
+        <v>177</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>74</v>
@@ -6985,21 +7061,23 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E59" s="2"/>
+      <c r="E59" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>74</v>
@@ -7011,10 +7089,12 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>234</v>
+        <v>180</v>
       </c>
       <c r="L59" s="2"/>
-      <c r="M59" s="2"/>
+      <c r="M59" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -7064,13 +7144,13 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>235</v>
+        <v>182</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>74</v>
@@ -7084,10 +7164,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7095,10 +7175,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>74</v>
@@ -7110,9 +7190,11 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L60" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7163,21 +7245,522 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="AG60" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK60" t="s" s="2">
+      <c r="M61" s="2"/>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L64" s="2"/>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK65" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T11:00:40+00:00</t>
+    <t>2025-02-18T15:10:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:10:02+00:00</t>
+    <t>2025-02-18T15:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:17:48+00:00</t>
+    <t>2025-02-18T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:09+00:00</t>
+    <t>2025-02-18T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:38+00:00</t>
+    <t>2025-02-18T15:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:24:54+00:00</t>
+    <t>2025-02-18T15:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:28:32+00:00</t>
+    <t>2025-02-18T15:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:29:38+00:00</t>
+    <t>2025-02-18T15:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:04+00:00</t>
+    <t>2025-02-18T15:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:23+00:00</t>
+    <t>2025-02-18T15:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:53+00:00</t>
+    <t>2025-02-20T13:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:34:17+00:00</t>
+    <t>2025-02-20T13:46:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:46:00+00:00</t>
+    <t>2025-02-20T13:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:48:47+00:00</t>
+    <t>2025-02-20T13:50:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:16+00:00</t>
+    <t>2025-02-20T13:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:51+00:00</t>
+    <t>2025-02-20T13:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:51:52+00:00</t>
+    <t>2025-02-20T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:17+00:00</t>
+    <t>2025-02-20T13:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:53+00:00</t>
+    <t>2025-02-20T14:37:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:37:28+00:00</t>
+    <t>2025-02-20T14:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:00+00:00</t>
+    <t>2025-02-20T14:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:23+00:00</t>
+    <t>2025-02-20T14:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:14+00:00</t>
+    <t>2025-02-20T14:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:55+00:00</t>
+    <t>2025-02-20T14:43:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:43:30+00:00</t>
+    <t>2025-02-20T14:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:45:32+00:00</t>
+    <t>2025-02-20T14:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:47:06+00:00</t>
+    <t>2025-02-20T14:48:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:48:16+00:00</t>
+    <t>2025-02-20T15:31:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T15:31:18+00:00</t>
+    <t>2025-02-21T13:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T13:12:29+00:00</t>
+    <t>2025-02-21T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T15:18:09+00:00</t>
+    <t>2025-02-23T14:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-23T14:02:58+00:00</t>
+    <t>2025-02-24T10:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T10:33:29+00:00</t>
+    <t>2025-02-24T11:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:08:59+00:00</t>
+    <t>2025-02-24T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T14:08:41+00:00</t>
+    <t>2025-02-25T09:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
